--- a/tools/importer/reports/import-hair-color.report.xlsx
+++ b/tools/importer/reports/import-hair-color.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="113">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,15 +61,33 @@
     <t>https://rouxbeauty.com/about-roux/</t>
   </si>
   <si>
+    <t>hair-care.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>hair-care</t>
+  </si>
+  <si>
+    <t>hair-color</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:32.228Z</t>
+  </si>
+  <si>
+    <t>Hair Care - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/</t>
+  </si>
+  <si>
     <t>hair-color.report.json</t>
   </si>
   <si>
     <t>["carousel-category","cards-category"]</t>
   </si>
   <si>
-    <t>hair-color</t>
-  </si>
-  <si>
     <t>2026-05-20T08:23:53.794Z</t>
   </si>
   <si>
@@ -116,6 +134,222 @@
   </si>
   <si>
     <t>https://rouxbeauty.com/top-sellers/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:38.336Z</t>
+  </si>
+  <si>
+    <t>Rejuvenating - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/</t>
+  </si>
+  <si>
+    <t>hair-care/repair-and-shine.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/repair-and-shine</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:46.367Z</t>
+  </si>
+  <si>
+    <t>Repair &amp; Shine - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/repair-and-shine/</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:51.886Z</t>
+  </si>
+  <si>
+    <t>Weightless Oils - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/weightless-oils/</t>
+  </si>
+  <si>
+    <t>hair-color/clean-touch-stain-remover.report.json</t>
+  </si>
+  <si>
+    <t>["columns-product","tabs-product"]</t>
+  </si>
+  <si>
+    <t>hair-color/clean-touch-stain-remover</t>
+  </si>
+  <si>
+    <t>product-page</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:28.866Z</t>
+  </si>
+  <si>
+    <t>Clean Touch Stain Remover - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-color/clean-touch-stain-remover/</t>
+  </si>
+  <si>
+    <t>hair-color/fanci-full-rinse.report.json</t>
+  </si>
+  <si>
+    <t>hair-color/fanci-full-rinse</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:16.344Z</t>
+  </si>
+  <si>
+    <t>Fanci-Full Rinse - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-color/fanci-full-rinse/</t>
+  </si>
+  <si>
+    <t>hair-color/tween-time.report.json</t>
+  </si>
+  <si>
+    <t>hair-color/tween-time</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:22.194Z</t>
+  </si>
+  <si>
+    <t>‘Tween Time - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-color/tween-time/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:57.283Z</t>
+  </si>
+  <si>
+    <t>Anti-Aging Leave-In Treatments - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/leave-in-treatments/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/porosity-control.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/porosity-control</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:34.795Z</t>
+  </si>
+  <si>
+    <t>Rejuvenating Porosity Control Corrector &amp; Conditioner - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/porosity-control/</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/luminous-shampoo.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/luminous-shampoo</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:00.514Z</t>
+  </si>
+  <si>
+    <t>Weightless Precious Oils Collection Luminous Shampoo - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/weightless-oils/luminous-shampoo/</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/restorative-hair-masque.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/restorative-hair-masque</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:15.070Z</t>
+  </si>
+  <si>
+    <t>Weightless Precious Oils Collection Restorative Hair Masque - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/weightless-oils/restorative-hair-masque/</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/softening-conditioner.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/weightless-oils/softening-conditioner</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:51:07.640Z</t>
+  </si>
+  <si>
+    <t>Weightless Precious Oils Collection Softening Conditioner - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/weightless-oils/softening-conditioner/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/07-extra-volume.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/07-extra-volume</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:47.151Z</t>
+  </si>
+  <si>
+    <t>07 Anti-Aging Extra Volume Leave-In Treatment - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/leave-in-treatments/07-extra-volume/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/233-extra-repair.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/233-extra-repair</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:40.517Z</t>
+  </si>
+  <si>
+    <t>233 Anti-Aging Extra Repair Leave-In Treatment - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/leave-in-treatments/233-extra-repair/</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/hair-and-scalp-rehab.report.json</t>
+  </si>
+  <si>
+    <t>hair-care/rejuvenating/leave-in-treatments/hair-and-scalp-rehab</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:50:53.988Z</t>
+  </si>
+  <si>
+    <t>Anti-Aging Hair &amp; Scalp Rehab Leave-In Treatment - RouxBeauty.com</t>
+  </si>
+  <si>
+    <t>https://rouxbeauty.com/hair-care/rejuvenating/leave-in-treatments/hair-and-scalp-rehab/</t>
   </si>
 </sst>
 </file>
@@ -504,16 +738,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="37" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -582,53 +813,53 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -644,6 +875,396 @@
       </c>
       <c r="H5" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
